--- a/Results.xlsx
+++ b/Results.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\研究生的资料\聚类\双自表达加张量\Upload_code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA4D5BC1-695A-4646-85CC-D293A4C43606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{309239F1-844C-4500-80CC-05ED9F9DDDD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2880" yWindow="4215" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31680" yWindow="3900" windowWidth="21600" windowHeight="11385"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" fullCalcOnLoad="true"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,19 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+  <si>
+    <t>NGs.mat</t>
+  </si>
+  <si>
+    <t>yale_mtv.mat</t>
+  </si>
+  <si>
+    <t>NGs.mat</t>
+  </si>
+  <si>
+    <t>yale_mtv.mat</t>
+  </si>
   <si>
     <t>NGs.mat</t>
   </si>
@@ -61,7 +73,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -69,12 +81,54 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -355,23 +409,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.875" customWidth="1"/>
-    <col min="2" max="2" width="6.5" customWidth="1"/>
-    <col min="3" max="3" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="4.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="6.5" customWidth="1"/>
-    <col min="11" max="17" width="12.5" customWidth="1"/>
+    <col min="1" max="1" width="11.875" customWidth="true"/>
+    <col min="2" max="2" width="6.5" customWidth="true"/>
+    <col min="3" max="3" width="5.5" bestFit="true" customWidth="true"/>
+    <col min="4" max="4" width="3.5" bestFit="true" customWidth="true"/>
+    <col min="7" max="7" width="6.5" customWidth="true"/>
+    <col min="11" max="11" width="2.125" customWidth="true"/>
+    <col min="5" max="5" width="3.5" bestFit="true" customWidth="true"/>
+    <col min="6" max="6" width="3.5" bestFit="true" customWidth="true"/>
+    <col min="8" max="8" width="6.5" customWidth="true"/>
+    <col min="9" max="9" width="6.5" customWidth="true"/>
+    <col min="10" max="10" width="6.5" customWidth="true"/>
+    <col min="12" max="12" width="2.125" customWidth="true"/>
+    <col min="13" max="13" width="2.125" customWidth="true"/>
+    <col min="14" max="14" width="2.125" customWidth="true"/>
+    <col min="15" max="15" width="2.125" customWidth="true"/>
+    <col min="16" max="16" width="2.125" customWidth="true"/>
+    <col min="17" max="17" width="2.125" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -424,12 +489,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="4" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
@@ -461,77 +526,140 @@
         <v>1E-4</v>
       </c>
       <c r="K4">
-        <v>0.9939393939393939</v>
+        <v>1</v>
       </c>
       <c r="L4">
-        <v>0.99239783918806268</v>
+        <v>1</v>
       </c>
       <c r="M4">
-        <v>0.9939393939393939</v>
+        <v>1</v>
       </c>
       <c r="N4">
-        <v>0.9872804360993338</v>
+        <v>1</v>
       </c>
       <c r="O4">
-        <v>0.98668280871670699</v>
+        <v>1</v>
       </c>
       <c r="P4">
-        <v>0.98645395761551891</v>
+        <v>1</v>
       </c>
       <c r="Q4">
-        <v>0.98787878787878791</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5">
-        <v>1E-4</v>
-      </c>
-      <c r="C5">
-        <v>0.1</v>
-      </c>
-      <c r="D5">
-        <v>0.1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>1.6</v>
-      </c>
-      <c r="G5">
-        <v>1E-4</v>
-      </c>
-      <c r="H5">
-        <v>1E-4</v>
-      </c>
-      <c r="I5">
-        <v>1E-4</v>
-      </c>
-      <c r="J5">
-        <v>1E-4</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-      <c r="N5">
-        <v>1</v>
-      </c>
-      <c r="O5">
-        <v>1</v>
-      </c>
-      <c r="P5">
-        <v>1</v>
-      </c>
-      <c r="Q5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0">
+        <v>1</v>
+      </c>
+      <c r="B7" s="0">
+        <v>1.0000000000000001e-05</v>
+      </c>
+      <c r="C7" s="0">
+        <v>0.001</v>
+      </c>
+      <c r="D7" s="0">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="E7" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="F7" s="0">
+        <v>1.6000000000000001</v>
+      </c>
+      <c r="G7" s="0">
+        <v>0.0001</v>
+      </c>
+      <c r="H7" s="0">
+        <v>0.0001</v>
+      </c>
+      <c r="I7" s="0">
+        <v>0.0001</v>
+      </c>
+      <c r="J7" s="0">
+        <v>0.0001</v>
+      </c>
+      <c r="K7" s="0">
+        <v>1</v>
+      </c>
+      <c r="L7" s="0">
+        <v>1</v>
+      </c>
+      <c r="M7" s="0">
+        <v>1</v>
+      </c>
+      <c r="N7" s="0">
+        <v>1</v>
+      </c>
+      <c r="O7" s="0">
+        <v>1</v>
+      </c>
+      <c r="P7" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0">
+        <v>1</v>
+      </c>
+      <c r="B9" s="0">
+        <v>0.0001</v>
+      </c>
+      <c r="C9" s="0">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="D9" s="0">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="E9" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="F9" s="0">
+        <v>1.6000000000000001</v>
+      </c>
+      <c r="G9" s="0">
+        <v>0.0001</v>
+      </c>
+      <c r="H9" s="0">
+        <v>0.0001</v>
+      </c>
+      <c r="I9" s="0">
+        <v>0.0001</v>
+      </c>
+      <c r="J9" s="0">
+        <v>0.0001</v>
+      </c>
+      <c r="K9" s="0">
+        <v>1</v>
+      </c>
+      <c r="L9" s="0">
+        <v>1</v>
+      </c>
+      <c r="M9" s="0">
+        <v>1</v>
+      </c>
+      <c r="N9" s="0">
+        <v>1</v>
+      </c>
+      <c r="O9" s="0">
+        <v>1</v>
+      </c>
+      <c r="P9" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="0">
         <v>1</v>
       </c>
     </row>
